--- a/artfynd/A 6485-2026 artfynd.xlsx
+++ b/artfynd/A 6485-2026 artfynd.xlsx
@@ -1083,45 +1083,65 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131697093</v>
+        <v>131697070</v>
       </c>
       <c r="B6" t="n">
-        <v>79260</v>
+        <v>99033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510844</v>
+        <v>511000</v>
       </c>
       <c r="R6" t="n">
-        <v>6989976</v>
+        <v>6989718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Minst 18 plantor inom ca 1 m2 yta i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1167,8 +1187,14 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1185,45 +1211,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131697089</v>
+        <v>131697058</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>80393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510656</v>
+        <v>510962</v>
       </c>
       <c r="R7" t="n">
-        <v>6990107</v>
+        <v>6989759</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,19 +1287,20 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1287,48 +1317,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131697058</v>
+        <v>131697089</v>
       </c>
       <c r="B8" t="n">
-        <v>80393</v>
+        <v>79260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510962</v>
+        <v>510656</v>
       </c>
       <c r="R8" t="n">
-        <v>6989759</v>
+        <v>6990107</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,20 +1390,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1393,65 +1419,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131697070</v>
+        <v>131697093</v>
       </c>
       <c r="B9" t="n">
-        <v>99033</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511000</v>
+        <v>510844</v>
       </c>
       <c r="R9" t="n">
-        <v>6989718</v>
+        <v>6989976</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 18 plantor inom ca 1 m2 yta i äldre flerskiktad granskog.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1497,14 +1503,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131697101</v>
+        <v>131697062</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,34 +1532,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511015</v>
+        <v>510962</v>
       </c>
       <c r="R10" t="n">
-        <v>6989809</v>
+        <v>6989762</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1603,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rätt rikligt med lunglav på en björk.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1605,8 +1612,39 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad naturskog.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1725,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131697062</v>
+        <v>131697101</v>
       </c>
       <c r="B12" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,41 +1774,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510962</v>
+        <v>511015</v>
       </c>
       <c r="R12" t="n">
-        <v>6989762</v>
+        <v>6989809</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,7 +1838,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rätt rikligt med lunglav på en björk.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,39 +1847,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad naturskog.</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1865,45 +1865,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131697084</v>
+        <v>131697050</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>80394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510999</v>
+        <v>510854</v>
       </c>
       <c r="R13" t="n">
-        <v>6989899</v>
+        <v>6989981</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,19 +1945,40 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1967,52 +1995,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131697050</v>
+        <v>131697084</v>
       </c>
       <c r="B14" t="n">
-        <v>80394</v>
+        <v>79260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510854</v>
+        <v>510999</v>
       </c>
       <c r="R14" t="n">
-        <v>6989981</v>
+        <v>6989899</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,40 +2068,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2097,65 +2097,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131697068</v>
+        <v>131697061</v>
       </c>
       <c r="B15" t="n">
-        <v>99033</v>
+        <v>80365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510787</v>
+        <v>510852</v>
       </c>
       <c r="R15" t="n">
-        <v>6990044</v>
+        <v>6989978</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2192,7 +2175,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 2 m2 yta i gammal granskog.</t>
+          <t>Växer här på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2210,9 +2193,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2332,48 +2330,65 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131697061</v>
+        <v>131697068</v>
       </c>
       <c r="B17" t="n">
-        <v>80365</v>
+        <v>99033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510852</v>
+        <v>510787</v>
       </c>
       <c r="R17" t="n">
-        <v>6989978</v>
+        <v>6990044</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2410,7 +2425,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Växer här på en lutande sälg.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2428,24 +2443,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2463,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131697090</v>
+        <v>131697048</v>
       </c>
       <c r="B18" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2474,34 +2474,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510720</v>
+        <v>510978</v>
       </c>
       <c r="R18" t="n">
-        <v>6990065</v>
+        <v>6989754</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2538,7 +2546,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran. Mycket högt livsmiljövärde för tretåig hackspett baserat på stående död ved kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2549,6 +2557,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2667,49 +2695,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131697056</v>
+        <v>131697098</v>
       </c>
       <c r="B20" t="n">
-        <v>97898</v>
+        <v>79260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511009</v>
+        <v>510894</v>
       </c>
       <c r="R20" t="n">
-        <v>6989723</v>
+        <v>6989831</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,20 +2768,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2774,10 +2797,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131697048</v>
+        <v>131697090</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,42 +2808,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510978</v>
+        <v>510720</v>
       </c>
       <c r="R21" t="n">
-        <v>6989754</v>
+        <v>6990065</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2857,7 +2872,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran. Mycket högt livsmiljövärde för tretåig hackspett baserat på stående död ved kring fyndplatsen.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2868,26 +2883,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2904,45 +2899,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131697098</v>
+        <v>131697056</v>
       </c>
       <c r="B22" t="n">
-        <v>79260</v>
+        <v>97898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510894</v>
+        <v>511009</v>
       </c>
       <c r="R22" t="n">
-        <v>6989831</v>
+        <v>6989723</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2977,19 +2976,20 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3210,7 +3210,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131697080</v>
+        <v>131697079</v>
       </c>
       <c r="B25" t="n">
         <v>79260</v>
@@ -3245,10 +3245,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511045</v>
+        <v>511078</v>
       </c>
       <c r="R25" t="n">
-        <v>6990016</v>
+        <v>6989981</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3516,7 +3516,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131697079</v>
+        <v>131697080</v>
       </c>
       <c r="B28" t="n">
         <v>79260</v>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511078</v>
+        <v>511045</v>
       </c>
       <c r="R28" t="n">
-        <v>6989981</v>
+        <v>6990016</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3618,10 +3618,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131697082</v>
+        <v>131697044</v>
       </c>
       <c r="B29" t="n">
-        <v>79260</v>
+        <v>91828</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,34 +3629,41 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511027</v>
+        <v>511055</v>
       </c>
       <c r="R29" t="n">
-        <v>6989977</v>
+        <v>6989882</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,19 +3698,40 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar. 500 bålar. Mmm</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3720,10 +3748,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131697044</v>
+        <v>131697082</v>
       </c>
       <c r="B30" t="n">
-        <v>91828</v>
+        <v>79260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3731,41 +3759,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511055</v>
+        <v>511027</v>
       </c>
       <c r="R30" t="n">
-        <v>6989882</v>
+        <v>6989977</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3800,40 +3821,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar. 500 bålar. Mmm</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4117,45 +4117,61 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131697094</v>
+        <v>131697051</v>
       </c>
       <c r="B33" t="n">
-        <v>79260</v>
+        <v>57739</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510881</v>
+        <v>510980</v>
       </c>
       <c r="R33" t="n">
-        <v>6989897</v>
+        <v>6989683</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4190,11 +4206,6 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4203,6 +4214,16 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Gammal grannaturskog.</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4219,61 +4240,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131697051</v>
+        <v>131697096</v>
       </c>
       <c r="B34" t="n">
-        <v>57739</v>
+        <v>79260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>510980</v>
+        <v>510953</v>
       </c>
       <c r="R34" t="n">
-        <v>6989683</v>
+        <v>6989770</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4308,6 +4313,11 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4316,16 +4326,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Gammal grannaturskog.</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4342,7 +4342,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131697096</v>
+        <v>131697094</v>
       </c>
       <c r="B35" t="n">
         <v>79260</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>510953</v>
+        <v>510881</v>
       </c>
       <c r="R35" t="n">
-        <v>6989770</v>
+        <v>6989897</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4444,49 +4444,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131697054</v>
+        <v>131697081</v>
       </c>
       <c r="B36" t="n">
-        <v>97898</v>
+        <v>79260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>511073</v>
+        <v>511000</v>
       </c>
       <c r="R36" t="n">
-        <v>6989919</v>
+        <v>6990002</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4521,20 +4517,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4551,7 +4546,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131697081</v>
+        <v>131697097</v>
       </c>
       <c r="B37" t="n">
         <v>79260</v>
@@ -4586,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>511000</v>
+        <v>510955</v>
       </c>
       <c r="R37" t="n">
-        <v>6990002</v>
+        <v>6989789</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4626,7 +4621,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4653,45 +4648,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131697097</v>
+        <v>131697054</v>
       </c>
       <c r="B38" t="n">
-        <v>79260</v>
+        <v>97898</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>510955</v>
+        <v>511073</v>
       </c>
       <c r="R38" t="n">
-        <v>6989789</v>
+        <v>6989919</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4726,19 +4725,20 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4755,7 +4755,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131697099</v>
+        <v>131697086</v>
       </c>
       <c r="B39" t="n">
         <v>79260</v>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>510932</v>
+        <v>510843</v>
       </c>
       <c r="R39" t="n">
-        <v>6989835</v>
+        <v>6990054</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4857,10 +4857,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131697060</v>
+        <v>131697099</v>
       </c>
       <c r="B40" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4868,37 +4868,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>510856</v>
+        <v>510932</v>
       </c>
       <c r="R40" t="n">
-        <v>6989981</v>
+        <v>6989835</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4935,7 +4932,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Lunglav på en rakväxt yngre sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4944,39 +4941,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad naturskog.</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4993,10 +4959,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131697086</v>
+        <v>131697060</v>
       </c>
       <c r="B41" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5004,34 +4970,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>510843</v>
+        <v>510856</v>
       </c>
       <c r="R41" t="n">
-        <v>6990054</v>
+        <v>6989981</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5068,7 +5037,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Lunglav på en rakväxt yngre sälg.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5077,8 +5046,39 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad naturskog.</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5197,41 +5197,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131697063</v>
+        <v>131697055</v>
       </c>
       <c r="B43" t="n">
-        <v>80365</v>
+        <v>97898</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5239,10 +5236,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>510941</v>
+        <v>510920</v>
       </c>
       <c r="R43" t="n">
-        <v>6989742</v>
+        <v>6989845</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5277,11 +5274,6 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt med lunglavsbålar på en sälg.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5295,26 +5287,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5458,38 +5430,41 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131697055</v>
+        <v>131697063</v>
       </c>
       <c r="B45" t="n">
-        <v>97898</v>
+        <v>80365</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5497,10 +5472,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>510920</v>
+        <v>510941</v>
       </c>
       <c r="R45" t="n">
-        <v>6989845</v>
+        <v>6989742</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5535,6 +5510,11 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt med lunglavsbålar på en sälg.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5548,6 +5528,26 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 6485-2026 artfynd.xlsx
+++ b/artfynd/A 6485-2026 artfynd.xlsx
@@ -2463,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131697048</v>
+        <v>131697085</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2474,42 +2474,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510978</v>
+        <v>510862</v>
       </c>
       <c r="R18" t="n">
-        <v>6989754</v>
+        <v>6990025</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,7 +2538,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran. Mycket högt livsmiljövärde för tretåig hackspett baserat på stående död ved kring fyndplatsen.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,26 +2549,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2593,7 +2565,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131697085</v>
+        <v>131697098</v>
       </c>
       <c r="B19" t="n">
         <v>79260</v>
@@ -2628,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510862</v>
+        <v>510894</v>
       </c>
       <c r="R19" t="n">
-        <v>6990025</v>
+        <v>6989831</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2668,7 +2640,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,7 +2667,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131697098</v>
+        <v>131697090</v>
       </c>
       <c r="B20" t="n">
         <v>79260</v>
@@ -2730,10 +2702,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510894</v>
+        <v>510720</v>
       </c>
       <c r="R20" t="n">
-        <v>6989831</v>
+        <v>6990065</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2770,7 +2742,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2797,10 +2769,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131697090</v>
+        <v>131697048</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,34 +2780,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510720</v>
+        <v>510978</v>
       </c>
       <c r="R21" t="n">
-        <v>6990065</v>
+        <v>6989754</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,7 +2852,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran. Mycket högt livsmiljövärde för tretåig hackspett baserat på stående död ved kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2883,6 +2863,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3850,27 +3850,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131697047</v>
+        <v>131697053</v>
       </c>
       <c r="B31" t="n">
-        <v>57898</v>
+        <v>57739</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3878,25 +3878,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510816</v>
+        <v>511016</v>
       </c>
       <c r="R31" t="n">
-        <v>6990093</v>
+        <v>6989876</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3933,7 +3945,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>1 hane med sång hördes vid skymningstid.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3950,24 +3962,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad naturskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3985,27 +3982,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131697053</v>
+        <v>131697047</v>
       </c>
       <c r="B32" t="n">
-        <v>57739</v>
+        <v>57898</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4013,37 +4010,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511016</v>
+        <v>510816</v>
       </c>
       <c r="R32" t="n">
-        <v>6989876</v>
+        <v>6990093</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4080,7 +4065,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>1 hane med sång hördes vid skymningstid.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4097,9 +4082,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad naturskog.</t>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 6485-2026 artfynd.xlsx
+++ b/artfynd/A 6485-2026 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>131697070</v>
       </c>
       <c r="B6" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,48 +1211,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131697058</v>
+        <v>131697093</v>
       </c>
       <c r="B7" t="n">
-        <v>80393</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510962</v>
+        <v>510844</v>
       </c>
       <c r="R7" t="n">
-        <v>6989759</v>
+        <v>6989976</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,20 +1284,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1419,45 +1415,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131697093</v>
+        <v>131697058</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>80393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510844</v>
+        <v>510962</v>
       </c>
       <c r="R9" t="n">
-        <v>6989976</v>
+        <v>6989759</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,19 +1491,20 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131697062</v>
+        <v>131697101</v>
       </c>
       <c r="B10" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,41 +1532,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510962</v>
+        <v>511015</v>
       </c>
       <c r="R10" t="n">
-        <v>6989762</v>
+        <v>6989809</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rätt rikligt med lunglav på en björk.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,39 +1605,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad naturskog.</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1763,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131697101</v>
+        <v>131697062</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,34 +1736,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511015</v>
+        <v>510962</v>
       </c>
       <c r="R12" t="n">
-        <v>6989809</v>
+        <v>6989762</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1838,7 +1807,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rätt rikligt med lunglav på en björk.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,8 +1816,39 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad naturskog.</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2097,10 +2097,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131697061</v>
+        <v>131697091</v>
       </c>
       <c r="B15" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2108,37 +2108,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510852</v>
+        <v>510755</v>
       </c>
       <c r="R15" t="n">
-        <v>6989978</v>
+        <v>6990081</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2172,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Växer här på en lutande sälg.</t>
+          <t>Rikligt på många granar. 500 bålar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,34 +2181,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2228,10 +2199,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131697091</v>
+        <v>131697061</v>
       </c>
       <c r="B16" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2239,34 +2210,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510755</v>
+        <v>510852</v>
       </c>
       <c r="R16" t="n">
-        <v>6990081</v>
+        <v>6989978</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,7 +2277,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt på många granar. 500 bålar. Långväxta bålar.</t>
+          <t>Växer här på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2312,8 +2286,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2333,7 +2333,7 @@
         <v>131697068</v>
       </c>
       <c r="B17" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131697085</v>
+        <v>131697090</v>
       </c>
       <c r="B18" t="n">
         <v>79260</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510862</v>
+        <v>510720</v>
       </c>
       <c r="R18" t="n">
-        <v>6990025</v>
+        <v>6990065</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2667,7 +2667,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131697090</v>
+        <v>131697085</v>
       </c>
       <c r="B20" t="n">
         <v>79260</v>
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510720</v>
+        <v>510862</v>
       </c>
       <c r="R20" t="n">
-        <v>6990065</v>
+        <v>6990025</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2902,7 +2902,7 @@
         <v>131697056</v>
       </c>
       <c r="B22" t="n">
-        <v>97898</v>
+        <v>97899</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131697079</v>
+        <v>131697076</v>
       </c>
       <c r="B25" t="n">
         <v>79260</v>
@@ -3245,10 +3245,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511078</v>
+        <v>511060</v>
       </c>
       <c r="R25" t="n">
-        <v>6989981</v>
+        <v>6989867</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3312,7 +3312,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131697088</v>
+        <v>131697080</v>
       </c>
       <c r="B26" t="n">
         <v>79260</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>510688</v>
+        <v>511045</v>
       </c>
       <c r="R26" t="n">
-        <v>6990094</v>
+        <v>6990016</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3414,7 +3414,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131697076</v>
+        <v>131697088</v>
       </c>
       <c r="B27" t="n">
         <v>79260</v>
@@ -3449,10 +3449,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511060</v>
+        <v>510688</v>
       </c>
       <c r="R27" t="n">
-        <v>6989867</v>
+        <v>6990094</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3516,7 +3516,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131697080</v>
+        <v>131697079</v>
       </c>
       <c r="B28" t="n">
         <v>79260</v>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511045</v>
+        <v>511078</v>
       </c>
       <c r="R28" t="n">
-        <v>6990016</v>
+        <v>6989981</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3618,10 +3618,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131697044</v>
+        <v>131697082</v>
       </c>
       <c r="B29" t="n">
-        <v>91828</v>
+        <v>79260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,41 +3629,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511055</v>
+        <v>511027</v>
       </c>
       <c r="R29" t="n">
-        <v>6989882</v>
+        <v>6989977</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3698,40 +3691,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar. 500 bålar. Mmm</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3748,10 +3720,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131697082</v>
+        <v>131697044</v>
       </c>
       <c r="B30" t="n">
-        <v>79260</v>
+        <v>91828</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3759,34 +3731,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511027</v>
+        <v>511055</v>
       </c>
       <c r="R30" t="n">
-        <v>6989977</v>
+        <v>6989882</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3821,19 +3800,40 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar. 500 bålar. Mmm</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3850,27 +3850,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131697053</v>
+        <v>131697047</v>
       </c>
       <c r="B31" t="n">
-        <v>57739</v>
+        <v>57898</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3878,37 +3878,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511016</v>
+        <v>510816</v>
       </c>
       <c r="R31" t="n">
-        <v>6989876</v>
+        <v>6990093</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3945,7 +3933,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1 hane med sång hördes vid skymningstid.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3962,9 +3950,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad naturskog.</t>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3982,27 +3985,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131697047</v>
+        <v>131697053</v>
       </c>
       <c r="B32" t="n">
-        <v>57898</v>
+        <v>57739</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4010,25 +4013,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510816</v>
+        <v>511016</v>
       </c>
       <c r="R32" t="n">
-        <v>6990093</v>
+        <v>6989876</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4065,7 +4080,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>1 hane med sång hördes vid skymningstid.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4082,24 +4097,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad naturskog.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4117,61 +4117,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131697051</v>
+        <v>131697094</v>
       </c>
       <c r="B33" t="n">
-        <v>57739</v>
+        <v>79260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510980</v>
+        <v>510881</v>
       </c>
       <c r="R33" t="n">
-        <v>6989683</v>
+        <v>6989897</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4206,6 +4190,11 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4214,16 +4203,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Gammal grannaturskog.</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4342,45 +4321,61 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131697094</v>
+        <v>131697051</v>
       </c>
       <c r="B35" t="n">
-        <v>79260</v>
+        <v>57739</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>510881</v>
+        <v>510980</v>
       </c>
       <c r="R35" t="n">
-        <v>6989897</v>
+        <v>6989683</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4415,11 +4410,6 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4428,6 +4418,16 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Gammal grannaturskog.</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4444,7 +4444,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131697081</v>
+        <v>131697097</v>
       </c>
       <c r="B36" t="n">
         <v>79260</v>
@@ -4479,10 +4479,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>511000</v>
+        <v>510955</v>
       </c>
       <c r="R36" t="n">
-        <v>6990002</v>
+        <v>6989789</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4546,7 +4546,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131697097</v>
+        <v>131697081</v>
       </c>
       <c r="B37" t="n">
         <v>79260</v>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>510955</v>
+        <v>511000</v>
       </c>
       <c r="R37" t="n">
-        <v>6989789</v>
+        <v>6990002</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4651,7 +4651,7 @@
         <v>131697054</v>
       </c>
       <c r="B38" t="n">
-        <v>97898</v>
+        <v>97899</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131697086</v>
+        <v>131697060</v>
       </c>
       <c r="B39" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4766,34 +4766,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>510843</v>
+        <v>510856</v>
       </c>
       <c r="R39" t="n">
-        <v>6990054</v>
+        <v>6989981</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4830,7 +4833,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Lunglav på en rakväxt yngre sälg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4839,8 +4842,39 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad naturskog.</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4959,10 +4993,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131697060</v>
+        <v>131697086</v>
       </c>
       <c r="B41" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4970,37 +5004,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>510856</v>
+        <v>510843</v>
       </c>
       <c r="R41" t="n">
-        <v>6989981</v>
+        <v>6990054</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5037,7 +5068,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Lunglav på en rakväxt yngre sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5046,39 +5077,8 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad naturskog.</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5197,38 +5197,41 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131697055</v>
+        <v>131697063</v>
       </c>
       <c r="B43" t="n">
-        <v>97898</v>
+        <v>80365</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5236,10 +5239,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>510920</v>
+        <v>510941</v>
       </c>
       <c r="R43" t="n">
-        <v>6989845</v>
+        <v>6989742</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5274,6 +5277,11 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt med lunglavsbålar på en sälg.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5287,6 +5295,26 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5304,10 +5332,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131697059</v>
+        <v>131697103</v>
       </c>
       <c r="B44" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5315,37 +5343,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511080</v>
+        <v>511010</v>
       </c>
       <c r="R44" t="n">
-        <v>6989977</v>
+        <v>6989734</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5380,40 +5405,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt på en gran.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5430,7 +5434,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131697063</v>
+        <v>131697059</v>
       </c>
       <c r="B45" t="n">
         <v>80365</v>
@@ -5460,11 +5464,7 @@
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>510941</v>
+        <v>511080</v>
       </c>
       <c r="R45" t="n">
-        <v>6989742</v>
+        <v>6989977</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5508,11 +5508,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt med lunglavsbålar på en sälg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5565,45 +5560,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131697103</v>
+        <v>131697055</v>
       </c>
       <c r="B46" t="n">
-        <v>79260</v>
+        <v>97899</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>511010</v>
+        <v>510920</v>
       </c>
       <c r="R46" t="n">
-        <v>6989734</v>
+        <v>6989845</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5638,19 +5637,20 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt på en gran.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5670,7 +5670,7 @@
         <v>131697069</v>
       </c>
       <c r="B47" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 6485-2026 artfynd.xlsx
+++ b/artfynd/A 6485-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131697083</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131697095</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131697077</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>131697078</v>
       </c>
       <c r="B5" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,65 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131697070</v>
+        <v>131697093</v>
       </c>
       <c r="B6" t="n">
-        <v>99034</v>
+        <v>79261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511000</v>
+        <v>510844</v>
       </c>
       <c r="R6" t="n">
-        <v>6989718</v>
+        <v>6989976</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 18 plantor inom ca 1 m2 yta i äldre flerskiktad granskog.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1187,14 +1167,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1211,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131697093</v>
+        <v>131697089</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510844</v>
+        <v>510656</v>
       </c>
       <c r="R7" t="n">
-        <v>6989976</v>
+        <v>6990107</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,45 +1287,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131697089</v>
+        <v>131697058</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>80394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510656</v>
+        <v>510962</v>
       </c>
       <c r="R8" t="n">
-        <v>6990107</v>
+        <v>6989759</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,19 +1363,20 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1415,48 +1393,65 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131697058</v>
+        <v>131697070</v>
       </c>
       <c r="B9" t="n">
-        <v>80393</v>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510962</v>
+        <v>511000</v>
       </c>
       <c r="R9" t="n">
-        <v>6989759</v>
+        <v>6989718</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,6 +1484,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 1 m2 yta i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,7 +1524,7 @@
         <v>131697101</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>131697092</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>131697062</v>
       </c>
       <c r="B12" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>131697050</v>
       </c>
       <c r="B13" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>131697084</v>
       </c>
       <c r="B14" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2097,45 +2097,65 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131697091</v>
+        <v>131697068</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>99035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510755</v>
+        <v>510787</v>
       </c>
       <c r="R15" t="n">
-        <v>6990081</v>
+        <v>6990044</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,7 +2192,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt på många granar. 500 bålar. Långväxta bålar.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,8 +2201,19 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2199,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131697061</v>
+        <v>131697091</v>
       </c>
       <c r="B16" t="n">
-        <v>80365</v>
+        <v>79261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,37 +2241,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510852</v>
+        <v>510755</v>
       </c>
       <c r="R16" t="n">
-        <v>6989978</v>
+        <v>6990081</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2305,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Växer här på en lutande sälg.</t>
+          <t>Rikligt på många granar. 500 bålar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,34 +2314,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2330,65 +2332,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131697068</v>
+        <v>131697061</v>
       </c>
       <c r="B17" t="n">
-        <v>99034</v>
+        <v>80366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510787</v>
+        <v>510852</v>
       </c>
       <c r="R17" t="n">
-        <v>6990044</v>
+        <v>6989978</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2425,7 +2410,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 2 m2 yta i gammal granskog.</t>
+          <t>Växer här på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2443,9 +2428,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2463,45 +2463,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131697090</v>
+        <v>131697056</v>
       </c>
       <c r="B18" t="n">
-        <v>79260</v>
+        <v>97900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510720</v>
+        <v>511009</v>
       </c>
       <c r="R18" t="n">
-        <v>6990065</v>
+        <v>6989723</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2536,19 +2540,20 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt på gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2565,10 +2570,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131697098</v>
+        <v>131697048</v>
       </c>
       <c r="B19" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2576,34 +2581,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510894</v>
+        <v>510978</v>
       </c>
       <c r="R19" t="n">
-        <v>6989831</v>
+        <v>6989754</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2640,7 +2653,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack, äldre, på stambasen av en gran. Mycket högt livsmiljövärde för tretåig hackspett baserat på stående död ved kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2651,6 +2664,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2667,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131697085</v>
+        <v>131697090</v>
       </c>
       <c r="B20" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2702,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510862</v>
+        <v>510720</v>
       </c>
       <c r="R20" t="n">
-        <v>6990025</v>
+        <v>6990065</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2742,7 +2775,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2769,10 +2802,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131697048</v>
+        <v>131697098</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,42 +2813,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510978</v>
+        <v>510894</v>
       </c>
       <c r="R21" t="n">
-        <v>6989754</v>
+        <v>6989831</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2852,7 +2877,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran. Mycket högt livsmiljövärde för tretåig hackspett baserat på stående död ved kring fyndplatsen.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2863,26 +2888,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2899,49 +2904,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131697056</v>
+        <v>131697085</v>
       </c>
       <c r="B22" t="n">
-        <v>97899</v>
+        <v>79261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511009</v>
+        <v>510862</v>
       </c>
       <c r="R22" t="n">
-        <v>6989723</v>
+        <v>6990025</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2976,20 +2977,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3009,7 +3009,7 @@
         <v>131697087</v>
       </c>
       <c r="B23" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>131697102</v>
       </c>
       <c r="B24" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>131697076</v>
       </c>
       <c r="B25" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>131697080</v>
       </c>
       <c r="B26" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>131697088</v>
       </c>
       <c r="B27" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>131697079</v>
       </c>
       <c r="B28" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3618,10 +3618,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131697082</v>
+        <v>131697044</v>
       </c>
       <c r="B29" t="n">
-        <v>79260</v>
+        <v>91829</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,34 +3629,41 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511027</v>
+        <v>511055</v>
       </c>
       <c r="R29" t="n">
-        <v>6989977</v>
+        <v>6989882</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,19 +3698,40 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar. 500 bålar. Mmm</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3720,10 +3748,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131697044</v>
+        <v>131697082</v>
       </c>
       <c r="B30" t="n">
-        <v>91828</v>
+        <v>79261</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3731,41 +3759,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511055</v>
+        <v>511027</v>
       </c>
       <c r="R30" t="n">
-        <v>6989882</v>
+        <v>6989977</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3800,40 +3821,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar. 500 bålar. Mmm</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3850,27 +3850,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131697047</v>
+        <v>131697053</v>
       </c>
       <c r="B31" t="n">
-        <v>57898</v>
+        <v>57740</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3878,25 +3878,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510816</v>
+        <v>511016</v>
       </c>
       <c r="R31" t="n">
-        <v>6990093</v>
+        <v>6989876</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3933,7 +3945,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>1 hane med sång hördes vid skymningstid.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3950,24 +3962,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad naturskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3985,27 +3982,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131697053</v>
+        <v>131697047</v>
       </c>
       <c r="B32" t="n">
-        <v>57739</v>
+        <v>57899</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4013,37 +4010,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511016</v>
+        <v>510816</v>
       </c>
       <c r="R32" t="n">
-        <v>6989876</v>
+        <v>6990093</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4080,7 +4065,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>1 hane med sång hördes vid skymningstid.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4097,9 +4082,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad naturskog.</t>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4117,45 +4117,61 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131697094</v>
+        <v>131697051</v>
       </c>
       <c r="B33" t="n">
-        <v>79260</v>
+        <v>57740</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510881</v>
+        <v>510980</v>
       </c>
       <c r="R33" t="n">
-        <v>6989897</v>
+        <v>6989683</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4190,11 +4206,6 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4203,6 +4214,16 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Gammal grannaturskog.</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4219,10 +4240,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131697096</v>
+        <v>131697094</v>
       </c>
       <c r="B34" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4254,10 +4275,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>510953</v>
+        <v>510881</v>
       </c>
       <c r="R34" t="n">
-        <v>6989770</v>
+        <v>6989897</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4294,7 +4315,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4321,61 +4342,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131697051</v>
+        <v>131697096</v>
       </c>
       <c r="B35" t="n">
-        <v>57739</v>
+        <v>79261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>510980</v>
+        <v>510953</v>
       </c>
       <c r="R35" t="n">
-        <v>6989683</v>
+        <v>6989770</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4410,6 +4415,11 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4418,16 +4428,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Gammal grannaturskog.</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4447,7 +4447,7 @@
         <v>131697097</v>
       </c>
       <c r="B36" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>131697081</v>
       </c>
       <c r="B37" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>131697054</v>
       </c>
       <c r="B38" t="n">
-        <v>97899</v>
+        <v>97900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>131697060</v>
       </c>
       <c r="B39" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>131697099</v>
       </c>
       <c r="B40" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>131697086</v>
       </c>
       <c r="B41" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>131697100</v>
       </c>
       <c r="B42" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5197,41 +5197,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131697063</v>
+        <v>131697055</v>
       </c>
       <c r="B43" t="n">
-        <v>80365</v>
+        <v>97900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5239,10 +5236,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>510941</v>
+        <v>510920</v>
       </c>
       <c r="R43" t="n">
-        <v>6989742</v>
+        <v>6989845</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5277,11 +5274,6 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt med lunglavsbålar på en sälg.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5295,26 +5287,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5332,10 +5304,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131697103</v>
+        <v>131697063</v>
       </c>
       <c r="B44" t="n">
-        <v>79260</v>
+        <v>80366</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5343,34 +5315,41 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511010</v>
+        <v>510941</v>
       </c>
       <c r="R44" t="n">
-        <v>6989734</v>
+        <v>6989742</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5407,7 +5386,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt på en gran.</t>
+          <t>Hyfsat rikligt med lunglavsbålar på en sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5416,8 +5395,34 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5434,10 +5439,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131697059</v>
+        <v>131697103</v>
       </c>
       <c r="B45" t="n">
-        <v>80365</v>
+        <v>79261</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5445,37 +5450,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>511080</v>
+        <v>511010</v>
       </c>
       <c r="R45" t="n">
-        <v>6989977</v>
+        <v>6989734</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5510,40 +5512,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt på en gran.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5560,38 +5541,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131697055</v>
+        <v>131697059</v>
       </c>
       <c r="B46" t="n">
-        <v>97899</v>
+        <v>80366</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5599,10 +5579,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>510920</v>
+        <v>511080</v>
       </c>
       <c r="R46" t="n">
-        <v>6989845</v>
+        <v>6989977</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5650,6 +5630,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5670,7 +5670,7 @@
         <v>131697069</v>
       </c>
       <c r="B47" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>131697049</v>
       </c>
       <c r="B48" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 6485-2026 artfynd.xlsx
+++ b/artfynd/A 6485-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131697083</v>
       </c>
       <c r="B2" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131697095</v>
       </c>
       <c r="B3" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131697077</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>131697078</v>
       </c>
       <c r="B5" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>131697093</v>
       </c>
       <c r="B6" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>131697089</v>
       </c>
       <c r="B7" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>131697058</v>
       </c>
       <c r="B8" t="n">
-        <v>80394</v>
+        <v>80397</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>131697070</v>
       </c>
       <c r="B9" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>131697101</v>
       </c>
       <c r="B10" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>131697092</v>
       </c>
       <c r="B11" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>131697062</v>
       </c>
       <c r="B12" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>131697050</v>
       </c>
       <c r="B13" t="n">
-        <v>80395</v>
+        <v>80398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>131697084</v>
       </c>
       <c r="B14" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2097,65 +2097,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131697068</v>
+        <v>131697091</v>
       </c>
       <c r="B15" t="n">
-        <v>99035</v>
+        <v>79264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510787</v>
+        <v>510755</v>
       </c>
       <c r="R15" t="n">
-        <v>6990044</v>
+        <v>6990081</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2192,7 +2172,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 2 m2 yta i gammal granskog.</t>
+          <t>Rikligt på många granar. 500 bålar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,19 +2181,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2230,10 +2199,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131697091</v>
+        <v>131697061</v>
       </c>
       <c r="B16" t="n">
-        <v>79261</v>
+        <v>80369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2241,34 +2210,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510755</v>
+        <v>510852</v>
       </c>
       <c r="R16" t="n">
-        <v>6990081</v>
+        <v>6989978</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,7 +2277,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt på många granar. 500 bålar. Långväxta bålar.</t>
+          <t>Växer här på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,8 +2286,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2332,48 +2330,65 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131697061</v>
+        <v>131697068</v>
       </c>
       <c r="B17" t="n">
-        <v>80366</v>
+        <v>99038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510852</v>
+        <v>510787</v>
       </c>
       <c r="R17" t="n">
-        <v>6989978</v>
+        <v>6990044</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2410,7 +2425,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Växer här på en lutande sälg.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2428,24 +2443,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2463,49 +2463,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131697056</v>
+        <v>131697090</v>
       </c>
       <c r="B18" t="n">
-        <v>97900</v>
+        <v>79264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511009</v>
+        <v>510720</v>
       </c>
       <c r="R18" t="n">
-        <v>6989723</v>
+        <v>6990065</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2540,20 +2536,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt på gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2570,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131697048</v>
+        <v>131697098</v>
       </c>
       <c r="B19" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2581,42 +2576,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510978</v>
+        <v>510894</v>
       </c>
       <c r="R19" t="n">
-        <v>6989754</v>
+        <v>6989831</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2653,7 +2640,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran. Mycket högt livsmiljövärde för tretåig hackspett baserat på stående död ved kring fyndplatsen.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2664,26 +2651,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2700,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131697090</v>
+        <v>131697085</v>
       </c>
       <c r="B20" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2735,10 +2702,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510720</v>
+        <v>510862</v>
       </c>
       <c r="R20" t="n">
-        <v>6990065</v>
+        <v>6990025</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2775,7 +2742,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2802,10 +2769,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131697098</v>
+        <v>131697048</v>
       </c>
       <c r="B21" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,34 +2780,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510894</v>
+        <v>510978</v>
       </c>
       <c r="R21" t="n">
-        <v>6989831</v>
+        <v>6989754</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2877,7 +2852,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack, äldre, på stambasen av en gran. Mycket högt livsmiljövärde för tretåig hackspett baserat på stående död ved kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2888,6 +2863,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2904,45 +2899,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131697085</v>
+        <v>131697056</v>
       </c>
       <c r="B22" t="n">
-        <v>79261</v>
+        <v>97903</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510862</v>
+        <v>511009</v>
       </c>
       <c r="R22" t="n">
-        <v>6990025</v>
+        <v>6989723</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2977,19 +2976,20 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3009,7 +3009,7 @@
         <v>131697087</v>
       </c>
       <c r="B23" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>131697102</v>
       </c>
       <c r="B24" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>131697076</v>
       </c>
       <c r="B25" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>131697080</v>
       </c>
       <c r="B26" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>131697088</v>
       </c>
       <c r="B27" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>131697079</v>
       </c>
       <c r="B28" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>131697044</v>
       </c>
       <c r="B29" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>131697082</v>
       </c>
       <c r="B30" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>131697053</v>
       </c>
       <c r="B31" t="n">
-        <v>57740</v>
+        <v>57743</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>131697047</v>
       </c>
       <c r="B32" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4117,61 +4117,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131697051</v>
+        <v>131697094</v>
       </c>
       <c r="B33" t="n">
-        <v>57740</v>
+        <v>79264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510980</v>
+        <v>510881</v>
       </c>
       <c r="R33" t="n">
-        <v>6989683</v>
+        <v>6989897</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4206,6 +4190,11 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4214,16 +4203,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Gammal grannaturskog.</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4240,10 +4219,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131697094</v>
+        <v>131697096</v>
       </c>
       <c r="B34" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,10 +4254,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>510881</v>
+        <v>510953</v>
       </c>
       <c r="R34" t="n">
-        <v>6989897</v>
+        <v>6989770</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4315,7 +4294,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4342,45 +4321,61 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131697096</v>
+        <v>131697051</v>
       </c>
       <c r="B35" t="n">
-        <v>79261</v>
+        <v>57743</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>510953</v>
+        <v>510980</v>
       </c>
       <c r="R35" t="n">
-        <v>6989770</v>
+        <v>6989683</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4415,11 +4410,6 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4428,6 +4418,16 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Gammal grannaturskog.</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4447,7 +4447,7 @@
         <v>131697097</v>
       </c>
       <c r="B36" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>131697081</v>
       </c>
       <c r="B37" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>131697054</v>
       </c>
       <c r="B38" t="n">
-        <v>97900</v>
+        <v>97903</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>131697060</v>
       </c>
       <c r="B39" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>131697099</v>
       </c>
       <c r="B40" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>131697086</v>
       </c>
       <c r="B41" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>131697100</v>
       </c>
       <c r="B42" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5197,38 +5197,41 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131697055</v>
+        <v>131697063</v>
       </c>
       <c r="B43" t="n">
-        <v>97900</v>
+        <v>80369</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5236,10 +5239,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>510920</v>
+        <v>510941</v>
       </c>
       <c r="R43" t="n">
-        <v>6989845</v>
+        <v>6989742</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5274,6 +5277,11 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt med lunglavsbålar på en sälg.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5287,6 +5295,26 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5304,10 +5332,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131697063</v>
+        <v>131697103</v>
       </c>
       <c r="B44" t="n">
-        <v>80366</v>
+        <v>79264</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5315,41 +5343,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>510941</v>
+        <v>511010</v>
       </c>
       <c r="R44" t="n">
-        <v>6989742</v>
+        <v>6989734</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5386,7 +5407,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt med lunglavsbålar på en sälg.</t>
+          <t>Rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5395,34 +5416,8 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5439,10 +5434,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131697103</v>
+        <v>131697059</v>
       </c>
       <c r="B45" t="n">
-        <v>79261</v>
+        <v>80369</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5450,34 +5445,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>511010</v>
+        <v>511080</v>
       </c>
       <c r="R45" t="n">
-        <v>6989734</v>
+        <v>6989977</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5512,19 +5510,40 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt på en gran.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5541,37 +5560,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131697059</v>
+        <v>131697055</v>
       </c>
       <c r="B46" t="n">
-        <v>80366</v>
+        <v>97903</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5579,10 +5599,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>511080</v>
+        <v>510920</v>
       </c>
       <c r="R46" t="n">
-        <v>6989977</v>
+        <v>6989845</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5630,26 +5650,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5670,7 +5670,7 @@
         <v>131697069</v>
       </c>
       <c r="B47" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>131697049</v>
       </c>
       <c r="B48" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 6485-2026 artfynd.xlsx
+++ b/artfynd/A 6485-2026 artfynd.xlsx
@@ -1185,45 +1185,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131697089</v>
+        <v>131697058</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>80397</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510656</v>
+        <v>510962</v>
       </c>
       <c r="R7" t="n">
-        <v>6990107</v>
+        <v>6989759</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,19 +1261,20 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1287,48 +1291,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131697058</v>
+        <v>131697089</v>
       </c>
       <c r="B8" t="n">
-        <v>80397</v>
+        <v>79264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510962</v>
+        <v>510656</v>
       </c>
       <c r="R8" t="n">
-        <v>6989759</v>
+        <v>6990107</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,20 +1364,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -2097,45 +2097,65 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131697091</v>
+        <v>131697068</v>
       </c>
       <c r="B15" t="n">
-        <v>79264</v>
+        <v>99038</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510755</v>
+        <v>510787</v>
       </c>
       <c r="R15" t="n">
-        <v>6990081</v>
+        <v>6990044</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,7 +2192,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt på många granar. 500 bålar. Långväxta bålar.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,8 +2201,19 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2199,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131697061</v>
+        <v>131697091</v>
       </c>
       <c r="B16" t="n">
-        <v>80369</v>
+        <v>79264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,37 +2241,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510852</v>
+        <v>510755</v>
       </c>
       <c r="R16" t="n">
-        <v>6989978</v>
+        <v>6990081</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2305,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Växer här på en lutande sälg.</t>
+          <t>Rikligt på många granar. 500 bålar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,34 +2314,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2330,65 +2332,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131697068</v>
+        <v>131697061</v>
       </c>
       <c r="B17" t="n">
-        <v>99038</v>
+        <v>80369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510787</v>
+        <v>510852</v>
       </c>
       <c r="R17" t="n">
-        <v>6990044</v>
+        <v>6989978</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2425,7 +2410,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 2 m2 yta i gammal granskog.</t>
+          <t>Växer här på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2443,9 +2428,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3618,10 +3618,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131697044</v>
+        <v>131697082</v>
       </c>
       <c r="B29" t="n">
-        <v>91832</v>
+        <v>79264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,41 +3629,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511055</v>
+        <v>511027</v>
       </c>
       <c r="R29" t="n">
-        <v>6989882</v>
+        <v>6989977</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3698,40 +3691,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar. 500 bålar. Mmm</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3748,10 +3720,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131697082</v>
+        <v>131697044</v>
       </c>
       <c r="B30" t="n">
-        <v>79264</v>
+        <v>91832</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3759,34 +3731,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511027</v>
+        <v>511055</v>
       </c>
       <c r="R30" t="n">
-        <v>6989977</v>
+        <v>6989882</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3821,19 +3800,40 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar. 500 bålar. Mmm</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3850,27 +3850,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131697053</v>
+        <v>131697047</v>
       </c>
       <c r="B31" t="n">
-        <v>57743</v>
+        <v>57902</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3878,37 +3878,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511016</v>
+        <v>510816</v>
       </c>
       <c r="R31" t="n">
-        <v>6989876</v>
+        <v>6990093</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3945,7 +3933,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1 hane med sång hördes vid skymningstid.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3962,9 +3950,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad naturskog.</t>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3982,27 +3985,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131697047</v>
+        <v>131697053</v>
       </c>
       <c r="B32" t="n">
-        <v>57902</v>
+        <v>57743</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4010,25 +4013,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510816</v>
+        <v>511016</v>
       </c>
       <c r="R32" t="n">
-        <v>6990093</v>
+        <v>6989876</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4065,7 +4080,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>1 hane med sång hördes vid skymningstid.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4082,24 +4097,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad naturskog.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 6485-2026 artfynd.xlsx
+++ b/artfynd/A 6485-2026 artfynd.xlsx
@@ -1185,48 +1185,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131697058</v>
+        <v>131697089</v>
       </c>
       <c r="B7" t="n">
-        <v>80397</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510962</v>
+        <v>510656</v>
       </c>
       <c r="R7" t="n">
-        <v>6989759</v>
+        <v>6990107</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,20 +1258,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1291,45 +1287,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131697089</v>
+        <v>131697058</v>
       </c>
       <c r="B8" t="n">
-        <v>79264</v>
+        <v>80397</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510656</v>
+        <v>510962</v>
       </c>
       <c r="R8" t="n">
-        <v>6990107</v>
+        <v>6989759</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,19 +1363,20 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -2769,42 +2769,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131697048</v>
+        <v>131697056</v>
       </c>
       <c r="B21" t="n">
-        <v>57902</v>
+        <v>97903</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2812,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510978</v>
+        <v>511009</v>
       </c>
       <c r="R21" t="n">
-        <v>6989754</v>
+        <v>6989723</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2850,38 +2846,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran. Mycket högt livsmiljövärde för tretåig hackspett baserat på stående död ved kring fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2899,38 +2876,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131697056</v>
+        <v>131697048</v>
       </c>
       <c r="B22" t="n">
-        <v>97903</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2938,10 +2919,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511009</v>
+        <v>510978</v>
       </c>
       <c r="R22" t="n">
-        <v>6989723</v>
+        <v>6989754</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2976,19 +2957,38 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran. Mycket högt livsmiljövärde för tretåig hackspett baserat på stående död ved kring fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3618,10 +3618,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131697082</v>
+        <v>131697044</v>
       </c>
       <c r="B29" t="n">
-        <v>79264</v>
+        <v>91832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,34 +3629,41 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511027</v>
+        <v>511055</v>
       </c>
       <c r="R29" t="n">
-        <v>6989977</v>
+        <v>6989882</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,19 +3698,40 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar. 500 bålar. Mmm</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3720,10 +3748,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131697044</v>
+        <v>131697082</v>
       </c>
       <c r="B30" t="n">
-        <v>91832</v>
+        <v>79264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3731,41 +3759,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511055</v>
+        <v>511027</v>
       </c>
       <c r="R30" t="n">
-        <v>6989882</v>
+        <v>6989977</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3800,40 +3821,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar. 500 bålar. Mmm</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">

--- a/artfynd/A 6485-2026 artfynd.xlsx
+++ b/artfynd/A 6485-2026 artfynd.xlsx
@@ -2097,65 +2097,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131697068</v>
+        <v>131697091</v>
       </c>
       <c r="B15" t="n">
-        <v>99038</v>
+        <v>79264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510787</v>
+        <v>510755</v>
       </c>
       <c r="R15" t="n">
-        <v>6990044</v>
+        <v>6990081</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2192,7 +2172,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 2 m2 yta i gammal granskog.</t>
+          <t>Rikligt på många granar. 500 bålar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,19 +2181,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2230,10 +2199,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131697091</v>
+        <v>131697061</v>
       </c>
       <c r="B16" t="n">
-        <v>79264</v>
+        <v>80369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2241,34 +2210,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510755</v>
+        <v>510852</v>
       </c>
       <c r="R16" t="n">
-        <v>6990081</v>
+        <v>6989978</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,7 +2277,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt på många granar. 500 bålar. Långväxta bålar.</t>
+          <t>Växer här på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,8 +2286,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2332,48 +2330,65 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131697061</v>
+        <v>131697068</v>
       </c>
       <c r="B17" t="n">
-        <v>80369</v>
+        <v>99038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510852</v>
+        <v>510787</v>
       </c>
       <c r="R17" t="n">
-        <v>6989978</v>
+        <v>6990044</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2410,7 +2425,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Växer här på en lutande sälg.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2428,24 +2443,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 6485-2026 artfynd.xlsx
+++ b/artfynd/A 6485-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131697083</v>
       </c>
       <c r="B2" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131697095</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131697077</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>131697078</v>
       </c>
       <c r="B5" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,45 +1083,65 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131697093</v>
+        <v>131697070</v>
       </c>
       <c r="B6" t="n">
-        <v>79264</v>
+        <v>99044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510844</v>
+        <v>511000</v>
       </c>
       <c r="R6" t="n">
-        <v>6989976</v>
+        <v>6989718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Minst 18 plantor inom ca 1 m2 yta i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1167,8 +1187,14 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1185,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131697089</v>
+        <v>131697093</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510656</v>
+        <v>510844</v>
       </c>
       <c r="R7" t="n">
-        <v>6990107</v>
+        <v>6989976</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,48 +1313,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131697058</v>
+        <v>131697089</v>
       </c>
       <c r="B8" t="n">
-        <v>80397</v>
+        <v>79266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510962</v>
+        <v>510656</v>
       </c>
       <c r="R8" t="n">
-        <v>6989759</v>
+        <v>6990107</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,20 +1386,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1393,65 +1415,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131697070</v>
+        <v>131697058</v>
       </c>
       <c r="B9" t="n">
-        <v>99038</v>
+        <v>80399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511000</v>
+        <v>510962</v>
       </c>
       <c r="R9" t="n">
-        <v>6989718</v>
+        <v>6989759</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,11 +1489,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 1 m2 yta i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,7 +1524,7 @@
         <v>131697101</v>
       </c>
       <c r="B10" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>131697092</v>
       </c>
       <c r="B11" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>131697062</v>
       </c>
       <c r="B12" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>131697050</v>
       </c>
       <c r="B13" t="n">
-        <v>80398</v>
+        <v>80400</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>131697084</v>
       </c>
       <c r="B14" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>131697091</v>
       </c>
       <c r="B15" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>131697061</v>
       </c>
       <c r="B16" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>131697068</v>
       </c>
       <c r="B17" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2463,45 +2463,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131697090</v>
+        <v>131697056</v>
       </c>
       <c r="B18" t="n">
-        <v>79264</v>
+        <v>97909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510720</v>
+        <v>511009</v>
       </c>
       <c r="R18" t="n">
-        <v>6990065</v>
+        <v>6989723</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2536,19 +2540,20 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt på gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2565,10 +2570,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131697098</v>
+        <v>131697090</v>
       </c>
       <c r="B19" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2600,10 +2605,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510894</v>
+        <v>510720</v>
       </c>
       <c r="R19" t="n">
-        <v>6989831</v>
+        <v>6990065</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2640,7 +2645,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,10 +2672,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131697085</v>
+        <v>131697098</v>
       </c>
       <c r="B20" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2702,10 +2707,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510862</v>
+        <v>510894</v>
       </c>
       <c r="R20" t="n">
-        <v>6990025</v>
+        <v>6989831</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2742,7 +2747,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2769,49 +2774,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131697056</v>
+        <v>131697085</v>
       </c>
       <c r="B21" t="n">
-        <v>97903</v>
+        <v>79266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511009</v>
+        <v>510862</v>
       </c>
       <c r="R21" t="n">
-        <v>6989723</v>
+        <v>6990025</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2846,20 +2847,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2879,7 +2879,7 @@
         <v>131697048</v>
       </c>
       <c r="B22" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>131697087</v>
       </c>
       <c r="B23" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>131697102</v>
       </c>
       <c r="B24" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>131697076</v>
       </c>
       <c r="B25" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>131697080</v>
       </c>
       <c r="B26" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>131697088</v>
       </c>
       <c r="B27" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>131697079</v>
       </c>
       <c r="B28" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>131697044</v>
       </c>
       <c r="B29" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>131697082</v>
       </c>
       <c r="B30" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3850,27 +3850,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131697047</v>
+        <v>131697053</v>
       </c>
       <c r="B31" t="n">
-        <v>57902</v>
+        <v>57745</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3878,25 +3878,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510816</v>
+        <v>511016</v>
       </c>
       <c r="R31" t="n">
-        <v>6990093</v>
+        <v>6989876</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3933,7 +3945,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>1 hane med sång hördes vid skymningstid.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3950,24 +3962,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad naturskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3985,27 +3982,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131697053</v>
+        <v>131697047</v>
       </c>
       <c r="B32" t="n">
-        <v>57743</v>
+        <v>57904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4013,37 +4010,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511016</v>
+        <v>510816</v>
       </c>
       <c r="R32" t="n">
-        <v>6989876</v>
+        <v>6990093</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4080,7 +4065,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>1 hane med sång hördes vid skymningstid.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4097,9 +4082,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad naturskog.</t>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4120,7 +4120,7 @@
         <v>131697094</v>
       </c>
       <c r="B33" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>131697096</v>
       </c>
       <c r="B34" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>131697051</v>
       </c>
       <c r="B35" t="n">
-        <v>57743</v>
+        <v>57745</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>131697097</v>
       </c>
       <c r="B36" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>131697081</v>
       </c>
       <c r="B37" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>131697054</v>
       </c>
       <c r="B38" t="n">
-        <v>97903</v>
+        <v>97909</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>131697060</v>
       </c>
       <c r="B39" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>131697099</v>
       </c>
       <c r="B40" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>131697086</v>
       </c>
       <c r="B41" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>131697100</v>
       </c>
       <c r="B42" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>131697063</v>
       </c>
       <c r="B43" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>131697103</v>
       </c>
       <c r="B44" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>131697059</v>
       </c>
       <c r="B45" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>131697055</v>
       </c>
       <c r="B46" t="n">
-        <v>97903</v>
+        <v>97909</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>131697069</v>
       </c>
       <c r="B47" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>131697049</v>
       </c>
       <c r="B48" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 6485-2026 artfynd.xlsx
+++ b/artfynd/A 6485-2026 artfynd.xlsx
@@ -1083,65 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131697070</v>
+        <v>131697093</v>
       </c>
       <c r="B6" t="n">
-        <v>99044</v>
+        <v>79266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511000</v>
+        <v>510844</v>
       </c>
       <c r="R6" t="n">
-        <v>6989718</v>
+        <v>6989976</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 18 plantor inom ca 1 m2 yta i äldre flerskiktad granskog.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1187,14 +1167,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1211,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131697093</v>
+        <v>131697089</v>
       </c>
       <c r="B7" t="n">
         <v>79266</v>
@@ -1246,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510844</v>
+        <v>510656</v>
       </c>
       <c r="R7" t="n">
-        <v>6989976</v>
+        <v>6990107</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,45 +1287,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131697089</v>
+        <v>131697058</v>
       </c>
       <c r="B8" t="n">
-        <v>79266</v>
+        <v>80399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510656</v>
+        <v>510962</v>
       </c>
       <c r="R8" t="n">
-        <v>6990107</v>
+        <v>6989759</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,19 +1363,20 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1415,48 +1393,65 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131697058</v>
+        <v>131697070</v>
       </c>
       <c r="B9" t="n">
-        <v>80399</v>
+        <v>99044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510962</v>
+        <v>511000</v>
       </c>
       <c r="R9" t="n">
-        <v>6989759</v>
+        <v>6989718</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,6 +1484,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 1 m2 yta i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2097,45 +2097,65 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131697091</v>
+        <v>131697068</v>
       </c>
       <c r="B15" t="n">
-        <v>79266</v>
+        <v>99044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510755</v>
+        <v>510787</v>
       </c>
       <c r="R15" t="n">
-        <v>6990081</v>
+        <v>6990044</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,7 +2192,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt på många granar. 500 bålar. Långväxta bålar.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,8 +2201,19 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2199,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131697061</v>
+        <v>131697091</v>
       </c>
       <c r="B16" t="n">
-        <v>80371</v>
+        <v>79266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,37 +2241,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510852</v>
+        <v>510755</v>
       </c>
       <c r="R16" t="n">
-        <v>6989978</v>
+        <v>6990081</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2305,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Växer här på en lutande sälg.</t>
+          <t>Rikligt på många granar. 500 bålar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,34 +2314,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2330,65 +2332,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131697068</v>
+        <v>131697061</v>
       </c>
       <c r="B17" t="n">
-        <v>99044</v>
+        <v>80371</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510787</v>
+        <v>510852</v>
       </c>
       <c r="R17" t="n">
-        <v>6990044</v>
+        <v>6989978</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2425,7 +2410,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 2 m2 yta i gammal granskog.</t>
+          <t>Växer här på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2443,9 +2428,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 6485-2026 artfynd.xlsx
+++ b/artfynd/A 6485-2026 artfynd.xlsx
@@ -4117,45 +4117,61 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131697094</v>
+        <v>131697051</v>
       </c>
       <c r="B33" t="n">
-        <v>79266</v>
+        <v>57745</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510881</v>
+        <v>510980</v>
       </c>
       <c r="R33" t="n">
-        <v>6989897</v>
+        <v>6989683</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4190,11 +4206,6 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4203,6 +4214,16 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Gammal grannaturskog.</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4219,7 +4240,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131697096</v>
+        <v>131697094</v>
       </c>
       <c r="B34" t="n">
         <v>79266</v>
@@ -4254,10 +4275,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>510953</v>
+        <v>510881</v>
       </c>
       <c r="R34" t="n">
-        <v>6989770</v>
+        <v>6989897</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4294,7 +4315,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4321,61 +4342,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131697051</v>
+        <v>131697096</v>
       </c>
       <c r="B35" t="n">
-        <v>57745</v>
+        <v>79266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>510980</v>
+        <v>510953</v>
       </c>
       <c r="R35" t="n">
-        <v>6989683</v>
+        <v>6989770</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4410,6 +4415,11 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4418,16 +4428,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Gammal grannaturskog.</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">

--- a/artfynd/A 6485-2026 artfynd.xlsx
+++ b/artfynd/A 6485-2026 artfynd.xlsx
@@ -3850,27 +3850,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131697053</v>
+        <v>131697047</v>
       </c>
       <c r="B31" t="n">
-        <v>57745</v>
+        <v>57904</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3878,37 +3878,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511016</v>
+        <v>510816</v>
       </c>
       <c r="R31" t="n">
-        <v>6989876</v>
+        <v>6990093</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3945,7 +3933,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1 hane med sång hördes vid skymningstid.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3962,9 +3950,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad naturskog.</t>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3982,27 +3985,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131697047</v>
+        <v>131697053</v>
       </c>
       <c r="B32" t="n">
-        <v>57904</v>
+        <v>57745</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4010,25 +4013,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510816</v>
+        <v>511016</v>
       </c>
       <c r="R32" t="n">
-        <v>6990093</v>
+        <v>6989876</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4065,7 +4080,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>1 hane med sång hördes vid skymningstid.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4082,24 +4097,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad naturskog.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4117,61 +4117,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131697051</v>
+        <v>131697094</v>
       </c>
       <c r="B33" t="n">
-        <v>57745</v>
+        <v>79266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510980</v>
+        <v>510881</v>
       </c>
       <c r="R33" t="n">
-        <v>6989683</v>
+        <v>6989897</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4206,6 +4190,11 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4214,16 +4203,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Gammal grannaturskog.</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4240,7 +4219,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131697094</v>
+        <v>131697096</v>
       </c>
       <c r="B34" t="n">
         <v>79266</v>
@@ -4275,10 +4254,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>510881</v>
+        <v>510953</v>
       </c>
       <c r="R34" t="n">
-        <v>6989897</v>
+        <v>6989770</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4315,7 +4294,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4342,45 +4321,61 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131697096</v>
+        <v>131697051</v>
       </c>
       <c r="B35" t="n">
-        <v>79266</v>
+        <v>57745</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>510953</v>
+        <v>510980</v>
       </c>
       <c r="R35" t="n">
-        <v>6989770</v>
+        <v>6989683</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4415,11 +4410,6 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4428,6 +4418,16 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Gammal grannaturskog.</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">

--- a/artfynd/A 6485-2026 artfynd.xlsx
+++ b/artfynd/A 6485-2026 artfynd.xlsx
@@ -2097,65 +2097,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131697068</v>
+        <v>131697091</v>
       </c>
       <c r="B15" t="n">
-        <v>99044</v>
+        <v>79266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510787</v>
+        <v>510755</v>
       </c>
       <c r="R15" t="n">
-        <v>6990044</v>
+        <v>6990081</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2192,7 +2172,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 2 m2 yta i gammal granskog.</t>
+          <t>Rikligt på många granar. 500 bålar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,19 +2181,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2230,10 +2199,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131697091</v>
+        <v>131697061</v>
       </c>
       <c r="B16" t="n">
-        <v>79266</v>
+        <v>80371</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2241,34 +2210,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510755</v>
+        <v>510852</v>
       </c>
       <c r="R16" t="n">
-        <v>6990081</v>
+        <v>6989978</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,7 +2277,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt på många granar. 500 bålar. Långväxta bålar.</t>
+          <t>Växer här på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,8 +2286,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2332,48 +2330,65 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131697061</v>
+        <v>131697068</v>
       </c>
       <c r="B17" t="n">
-        <v>80371</v>
+        <v>99044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510852</v>
+        <v>510787</v>
       </c>
       <c r="R17" t="n">
-        <v>6989978</v>
+        <v>6990044</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2410,7 +2425,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Växer här på en lutande sälg.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2428,24 +2443,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 6485-2026 artfynd.xlsx
+++ b/artfynd/A 6485-2026 artfynd.xlsx
@@ -2097,45 +2097,65 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131697091</v>
+        <v>131697068</v>
       </c>
       <c r="B15" t="n">
-        <v>79266</v>
+        <v>99044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510755</v>
+        <v>510787</v>
       </c>
       <c r="R15" t="n">
-        <v>6990081</v>
+        <v>6990044</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,7 +2192,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt på många granar. 500 bålar. Långväxta bålar.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,8 +2201,19 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2199,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131697061</v>
+        <v>131697091</v>
       </c>
       <c r="B16" t="n">
-        <v>80371</v>
+        <v>79266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,37 +2241,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510852</v>
+        <v>510755</v>
       </c>
       <c r="R16" t="n">
-        <v>6989978</v>
+        <v>6990081</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2305,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Växer här på en lutande sälg.</t>
+          <t>Rikligt på många granar. 500 bålar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,34 +2314,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2330,65 +2332,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131697068</v>
+        <v>131697061</v>
       </c>
       <c r="B17" t="n">
-        <v>99044</v>
+        <v>80371</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510787</v>
+        <v>510852</v>
       </c>
       <c r="R17" t="n">
-        <v>6990044</v>
+        <v>6989978</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2425,7 +2410,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 2 m2 yta i gammal granskog.</t>
+          <t>Växer här på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2443,9 +2428,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -4117,45 +4117,61 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131697094</v>
+        <v>131697051</v>
       </c>
       <c r="B33" t="n">
-        <v>79266</v>
+        <v>57745</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510881</v>
+        <v>510980</v>
       </c>
       <c r="R33" t="n">
-        <v>6989897</v>
+        <v>6989683</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4190,11 +4206,6 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4203,6 +4214,16 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Gammal grannaturskog.</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4219,7 +4240,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131697096</v>
+        <v>131697094</v>
       </c>
       <c r="B34" t="n">
         <v>79266</v>
@@ -4254,10 +4275,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>510953</v>
+        <v>510881</v>
       </c>
       <c r="R34" t="n">
-        <v>6989770</v>
+        <v>6989897</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4294,7 +4315,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4321,61 +4342,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131697051</v>
+        <v>131697096</v>
       </c>
       <c r="B35" t="n">
-        <v>57745</v>
+        <v>79266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>510980</v>
+        <v>510953</v>
       </c>
       <c r="R35" t="n">
-        <v>6989683</v>
+        <v>6989770</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4410,6 +4415,11 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4418,16 +4428,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Gammal grannaturskog.</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">

--- a/artfynd/A 6485-2026 artfynd.xlsx
+++ b/artfynd/A 6485-2026 artfynd.xlsx
@@ -3850,27 +3850,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131697047</v>
+        <v>131697053</v>
       </c>
       <c r="B31" t="n">
-        <v>57904</v>
+        <v>57745</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3878,25 +3878,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510816</v>
+        <v>511016</v>
       </c>
       <c r="R31" t="n">
-        <v>6990093</v>
+        <v>6989876</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3933,7 +3945,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>1 hane med sång hördes vid skymningstid.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3950,24 +3962,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad naturskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3985,27 +3982,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131697053</v>
+        <v>131697047</v>
       </c>
       <c r="B32" t="n">
-        <v>57745</v>
+        <v>57904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4013,37 +4010,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511016</v>
+        <v>510816</v>
       </c>
       <c r="R32" t="n">
-        <v>6989876</v>
+        <v>6990093</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4080,7 +4065,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>1 hane med sång hördes vid skymningstid.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4097,9 +4082,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad naturskog.</t>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 6485-2026 artfynd.xlsx
+++ b/artfynd/A 6485-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131697083</v>
       </c>
       <c r="B2" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131697095</v>
       </c>
       <c r="B3" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131697077</v>
       </c>
       <c r="B4" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>131697078</v>
       </c>
       <c r="B5" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,45 +1083,65 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131697093</v>
+        <v>131697070</v>
       </c>
       <c r="B6" t="n">
-        <v>79266</v>
+        <v>99047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510844</v>
+        <v>511000</v>
       </c>
       <c r="R6" t="n">
-        <v>6989976</v>
+        <v>6989718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Minst 18 plantor inom ca 1 m2 yta i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1167,8 +1187,14 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1185,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131697089</v>
+        <v>131697093</v>
       </c>
       <c r="B7" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510656</v>
+        <v>510844</v>
       </c>
       <c r="R7" t="n">
-        <v>6990107</v>
+        <v>6989976</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,48 +1313,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131697058</v>
+        <v>131697089</v>
       </c>
       <c r="B8" t="n">
-        <v>80399</v>
+        <v>79269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510962</v>
+        <v>510656</v>
       </c>
       <c r="R8" t="n">
-        <v>6989759</v>
+        <v>6990107</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,20 +1386,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1393,65 +1415,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131697070</v>
+        <v>131697058</v>
       </c>
       <c r="B9" t="n">
-        <v>99044</v>
+        <v>80402</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511000</v>
+        <v>510962</v>
       </c>
       <c r="R9" t="n">
-        <v>6989718</v>
+        <v>6989759</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,11 +1489,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 1 m2 yta i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,7 +1524,7 @@
         <v>131697101</v>
       </c>
       <c r="B10" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>131697092</v>
       </c>
       <c r="B11" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>131697062</v>
       </c>
       <c r="B12" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>131697050</v>
       </c>
       <c r="B13" t="n">
-        <v>80400</v>
+        <v>80403</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>131697084</v>
       </c>
       <c r="B14" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2097,65 +2097,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131697068</v>
+        <v>131697091</v>
       </c>
       <c r="B15" t="n">
-        <v>99044</v>
+        <v>79269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510787</v>
+        <v>510755</v>
       </c>
       <c r="R15" t="n">
-        <v>6990044</v>
+        <v>6990081</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2192,7 +2172,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 2 m2 yta i gammal granskog.</t>
+          <t>Rikligt på många granar. 500 bålar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,19 +2181,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2230,10 +2199,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131697091</v>
+        <v>131697061</v>
       </c>
       <c r="B16" t="n">
-        <v>79266</v>
+        <v>80374</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2241,34 +2210,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510755</v>
+        <v>510852</v>
       </c>
       <c r="R16" t="n">
-        <v>6990081</v>
+        <v>6989978</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,7 +2277,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt på många granar. 500 bålar. Långväxta bålar.</t>
+          <t>Växer här på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,8 +2286,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2332,48 +2330,65 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131697061</v>
+        <v>131697068</v>
       </c>
       <c r="B17" t="n">
-        <v>80371</v>
+        <v>99047</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510852</v>
+        <v>510787</v>
       </c>
       <c r="R17" t="n">
-        <v>6989978</v>
+        <v>6990044</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2410,7 +2425,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Växer här på en lutande sälg.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2428,24 +2443,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2463,49 +2463,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131697056</v>
+        <v>131697090</v>
       </c>
       <c r="B18" t="n">
-        <v>97909</v>
+        <v>79269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511009</v>
+        <v>510720</v>
       </c>
       <c r="R18" t="n">
-        <v>6989723</v>
+        <v>6990065</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2540,20 +2536,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt på gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2570,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131697090</v>
+        <v>131697098</v>
       </c>
       <c r="B19" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510720</v>
+        <v>510894</v>
       </c>
       <c r="R19" t="n">
-        <v>6990065</v>
+        <v>6989831</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2645,7 +2640,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt på gran.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2672,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131697098</v>
+        <v>131697085</v>
       </c>
       <c r="B20" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,10 +2702,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510894</v>
+        <v>510862</v>
       </c>
       <c r="R20" t="n">
-        <v>6989831</v>
+        <v>6990025</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2747,7 +2742,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2774,10 +2769,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131697085</v>
+        <v>131697048</v>
       </c>
       <c r="B21" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,34 +2780,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510862</v>
+        <v>510978</v>
       </c>
       <c r="R21" t="n">
-        <v>6990025</v>
+        <v>6989754</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2849,7 +2852,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på stambasen av en gran. Mycket högt livsmiljövärde för tretåig hackspett baserat på stående död ved kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2860,6 +2863,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2876,42 +2899,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131697048</v>
+        <v>131697056</v>
       </c>
       <c r="B22" t="n">
-        <v>57904</v>
+        <v>97912</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2919,10 +2938,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510978</v>
+        <v>511009</v>
       </c>
       <c r="R22" t="n">
-        <v>6989754</v>
+        <v>6989723</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2957,38 +2976,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran. Mycket högt livsmiljövärde för tretåig hackspett baserat på stående död ved kring fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3009,7 +3009,7 @@
         <v>131697087</v>
       </c>
       <c r="B23" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>131697102</v>
       </c>
       <c r="B24" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>131697076</v>
       </c>
       <c r="B25" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>131697080</v>
       </c>
       <c r="B26" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>131697088</v>
       </c>
       <c r="B27" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>131697079</v>
       </c>
       <c r="B28" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>131697044</v>
       </c>
       <c r="B29" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>131697082</v>
       </c>
       <c r="B30" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3850,27 +3850,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131697053</v>
+        <v>131697047</v>
       </c>
       <c r="B31" t="n">
-        <v>57745</v>
+        <v>57907</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3878,37 +3878,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511016</v>
+        <v>510816</v>
       </c>
       <c r="R31" t="n">
-        <v>6989876</v>
+        <v>6990093</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3945,7 +3933,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1 hane med sång hördes vid skymningstid.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3962,9 +3950,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad naturskog.</t>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3982,27 +3985,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131697047</v>
+        <v>131697053</v>
       </c>
       <c r="B32" t="n">
-        <v>57904</v>
+        <v>57748</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4010,25 +4013,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510816</v>
+        <v>511016</v>
       </c>
       <c r="R32" t="n">
-        <v>6990093</v>
+        <v>6989876</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4065,7 +4080,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>1 hane med sång hördes vid skymningstid.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4082,24 +4097,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad naturskog.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4117,61 +4117,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131697051</v>
+        <v>131697094</v>
       </c>
       <c r="B33" t="n">
-        <v>57745</v>
+        <v>79269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510980</v>
+        <v>510881</v>
       </c>
       <c r="R33" t="n">
-        <v>6989683</v>
+        <v>6989897</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4206,6 +4190,11 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4214,16 +4203,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Gammal grannaturskog.</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4240,10 +4219,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131697094</v>
+        <v>131697096</v>
       </c>
       <c r="B34" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,10 +4254,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>510881</v>
+        <v>510953</v>
       </c>
       <c r="R34" t="n">
-        <v>6989897</v>
+        <v>6989770</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4315,7 +4294,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4342,45 +4321,61 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131697096</v>
+        <v>131697051</v>
       </c>
       <c r="B35" t="n">
-        <v>79266</v>
+        <v>57748</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>510953</v>
+        <v>510980</v>
       </c>
       <c r="R35" t="n">
-        <v>6989770</v>
+        <v>6989683</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4415,11 +4410,6 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4428,6 +4418,16 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Gammal grannaturskog.</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4447,7 +4447,7 @@
         <v>131697097</v>
       </c>
       <c r="B36" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>131697081</v>
       </c>
       <c r="B37" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>131697054</v>
       </c>
       <c r="B38" t="n">
-        <v>97909</v>
+        <v>97912</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>131697060</v>
       </c>
       <c r="B39" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>131697099</v>
       </c>
       <c r="B40" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>131697086</v>
       </c>
       <c r="B41" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>131697100</v>
       </c>
       <c r="B42" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5197,41 +5197,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131697063</v>
+        <v>131697055</v>
       </c>
       <c r="B43" t="n">
-        <v>80371</v>
+        <v>97912</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5239,10 +5236,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>510941</v>
+        <v>510920</v>
       </c>
       <c r="R43" t="n">
-        <v>6989742</v>
+        <v>6989845</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5277,11 +5274,6 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt med lunglavsbålar på en sälg.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5295,26 +5287,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5332,10 +5304,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131697103</v>
+        <v>131697063</v>
       </c>
       <c r="B44" t="n">
-        <v>79266</v>
+        <v>80374</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5343,34 +5315,41 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511010</v>
+        <v>510941</v>
       </c>
       <c r="R44" t="n">
-        <v>6989734</v>
+        <v>6989742</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5407,7 +5386,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt på en gran.</t>
+          <t>Hyfsat rikligt med lunglavsbålar på en sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5416,8 +5395,34 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5434,10 +5439,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131697059</v>
+        <v>131697103</v>
       </c>
       <c r="B45" t="n">
-        <v>80371</v>
+        <v>79269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5445,37 +5450,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>511080</v>
+        <v>511010</v>
       </c>
       <c r="R45" t="n">
-        <v>6989977</v>
+        <v>6989734</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5510,40 +5512,19 @@
           <t>2026-03-16</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt på en gran.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5560,38 +5541,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131697055</v>
+        <v>131697059</v>
       </c>
       <c r="B46" t="n">
-        <v>97909</v>
+        <v>80374</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5599,10 +5579,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>510920</v>
+        <v>511080</v>
       </c>
       <c r="R46" t="n">
-        <v>6989845</v>
+        <v>6989977</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5650,6 +5630,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5670,7 +5670,7 @@
         <v>131697069</v>
       </c>
       <c r="B47" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>131697049</v>
       </c>
       <c r="B48" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
